--- a/data.xlsx
+++ b/data.xlsx
@@ -413,1186 +413,911 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data do registro</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Descrição</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Data do registro</t>
+          <t>Valor</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Descrição</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Dia de Pagamento</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Dia de Pagamento</t>
+          <t>Reserva de Emergência</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Viver de Renda</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Reserva de Emergência</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Viver de Renda</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
           <t>Aporte Mensal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Entradas</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Despesas</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supermercado</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>450</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Supermercado</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>450</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12000</v>
+      </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>240000</v>
       </c>
       <c r="I2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>200</v>
-      </c>
-      <c r="L2" t="n">
-        <v>335</v>
-      </c>
-      <c r="M2" t="n">
-        <v>14115</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Conta de Luz</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>180</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Conta de Luz</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>180</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>120</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>120</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>05/08/2027</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Condomínio</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>120</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Condomínio</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>120</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>600</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>600</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>08/08/2026</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>150</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>150</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>10/08/2028</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Freelance de Design</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>45</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Freelance de Design</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>45</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>Entrada</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Farmácia</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>800</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Farmácia</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>800</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>15/08/2026</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mensalidade Academia</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>85</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mensalidade Academia</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>85</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>16/08/2029</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cinema e Pipoca</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>110</v>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cinema e Pipoca</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>110</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>18/08/2026</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Plano de Saúde</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>60</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Plano de Saúde</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>25/08/2026</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Posto de Combustível</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>350</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Posto de Combustível</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>350</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>22/08/2030</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Venda de Bicicleta</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>200</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Venda de Bicicleta</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>200</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
           <t>Entrada</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>24/08/2026</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Assinatura Streaming</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>400</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Assinatura Streaming</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>400</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>25/08/2026</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supermercado</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>45</v>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Supermercado</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>45</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>26/08/2026</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Conta de Água</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>320</v>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Conta de Água</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>320</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>95</v>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pet Shop</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>95</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>17</v>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>30/08/2026</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Manutenção do Carro</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>130</v>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manutenção do Carro</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>130</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Presente de Aniversário</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5500</v>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Presente de Aniversário</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>5500</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IPTU</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>250</v>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IPTU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>250</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
           <t xml:space="preserve">Saída </t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>15/09/2026</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="n">
-        <v>20</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Café na Padaria</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>150</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Café na Padaria</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>150</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="n">
-        <v>21</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>07/09/2026</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Seguro Auto</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Seguro Auto</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>25</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>12/09/2026</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="n">
-        <v>22</v>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Curso Online</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>150</v>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Curso Online</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>150</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>15/09/2026</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="n">
-        <v>23</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>11/09/2034</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Compra de Roupas</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>25</v>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Compra de Roupas</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>25</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="n">
-        <v>24</v>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>14/09/2026</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Consulta Médica</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>220</v>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Consulta Médica</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>220</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="n">
-        <v>25</v>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>16/09/2026</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Reembolso do Plano</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>90</v>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Reembolso do Plano</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>90</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>Entrada</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="n">
-        <v>26</v>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>18/09/2035</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dentista</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>350</v>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Dentista</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>350</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="n">
-        <v>27</v>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>20/09/2026</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IPVA</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>250</v>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IPVA</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>250</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="n">
-        <v>28</v>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>16/08/2026</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1100</v>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aluguel</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="n">
-        <v>29</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Livro</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>30</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Livro</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>30</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="n">
-        <v>30</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>20/08/2026</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Videogame</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2000</v>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Videogame</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="n">
-        <v>31</v>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>50</v>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Comida</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>50</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>Aporte Mensal</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -495,6 +500,7 @@
       <c r="I2" t="n">
         <v>400</v>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +530,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,6 +560,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,6 +590,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +616,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -632,6 +642,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -657,6 +668,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +694,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -711,6 +724,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -736,6 +750,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -765,6 +780,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -790,6 +806,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -815,6 +832,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -844,6 +862,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -869,6 +888,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -898,6 +918,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -923,6 +944,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -948,6 +970,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -973,6 +996,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1002,6 +1026,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1027,6 +1052,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1056,6 +1082,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1085,6 +1112,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1110,6 +1138,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1135,6 +1164,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1160,6 +1190,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1185,6 +1216,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1214,6 +1246,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1243,6 +1276,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1268,6 +1302,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1293,6 +1328,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1318,6 +1354,71 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Videogame</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>50</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Conta de Luz</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>200</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Conta</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Contas de Casa</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
